--- a/03_Outputs/all/03_DS/ds_idx2_Adultez.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx2_Adultez.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6010168790327213</v>
+        <v>0.6010168790327229</v>
       </c>
       <c r="D2">
-        <v>-2.155179357369415</v>
+        <v>-2.155179357369417</v>
       </c>
       <c r="E2">
-        <v>-0.5995673596679615</v>
+        <v>-0.5995673596679577</v>
       </c>
       <c r="F2">
-        <v>-0.5787175700324483</v>
+        <v>-0.5787175700324463</v>
       </c>
       <c r="G2">
-        <v>0.3886561689079359</v>
+        <v>0.3886561689079377</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.7037793012201373</v>
+        <v>-0.703779301220137</v>
       </c>
       <c r="D3">
         <v>1.50004083407405</v>
       </c>
       <c r="E3">
-        <v>-0.004842397958427582</v>
+        <v>-0.004842397958430611</v>
       </c>
       <c r="F3">
-        <v>0.1531808230073014</v>
+        <v>0.1531808230072999</v>
       </c>
       <c r="G3">
-        <v>-0.3890442398252222</v>
+        <v>-0.389044239825222</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-2.293825235352616</v>
+        <v>-2.293825235352618</v>
       </c>
       <c r="D4">
-        <v>0.7982252658490849</v>
+        <v>0.7982252658490853</v>
       </c>
       <c r="E4">
-        <v>0.6981150373186734</v>
+        <v>0.6981150373186715</v>
       </c>
       <c r="F4">
-        <v>0.05863864823411767</v>
+        <v>0.05863864823411882</v>
       </c>
       <c r="G4">
-        <v>0.2797018666756576</v>
+        <v>0.2797018666756569</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-2.417442455825572</v>
+        <v>-2.417442455825573</v>
       </c>
       <c r="D5">
-        <v>-0.09552302332755659</v>
+        <v>-0.09552302332755636</v>
       </c>
       <c r="E5">
-        <v>0.3940170234273947</v>
+        <v>0.3940170234273937</v>
       </c>
       <c r="F5">
-        <v>0.5819886802188065</v>
+        <v>0.5819886802188046</v>
       </c>
       <c r="G5">
-        <v>-0.7727496665982541</v>
+        <v>-0.7727496665982565</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.52142807236598</v>
+        <v>1.521428072365983</v>
       </c>
       <c r="D6">
-        <v>0.2479723270019703</v>
+        <v>0.2479723270019693</v>
       </c>
       <c r="E6">
-        <v>-0.6330601186437362</v>
+        <v>-0.6330601186437365</v>
       </c>
       <c r="F6">
-        <v>-0.4803844268048561</v>
+        <v>-0.4803844268048552</v>
       </c>
       <c r="G6">
-        <v>0.3366975004580755</v>
+        <v>0.3366975004580781</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3577792633748268</v>
+        <v>-0.3577792633748267</v>
       </c>
       <c r="D7">
-        <v>0.5162576169266532</v>
+        <v>0.5162576169266533</v>
       </c>
       <c r="E7">
-        <v>0.4460273080769199</v>
+        <v>0.4460273080769191</v>
       </c>
       <c r="F7">
-        <v>-0.6443041420906457</v>
+        <v>-0.6443041420906452</v>
       </c>
       <c r="G7">
-        <v>0.1650968129726625</v>
+        <v>0.1650968129726649</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>1.182224938379926</v>
+        <v>1.182224938379928</v>
       </c>
       <c r="D8">
-        <v>0.5363663804056622</v>
+        <v>0.5363663804056602</v>
       </c>
       <c r="E8">
-        <v>-1.314759595885209</v>
+        <v>-1.31475959588521</v>
       </c>
       <c r="F8">
-        <v>-0.1043677499786114</v>
+        <v>-0.1043677499786094</v>
       </c>
       <c r="G8">
-        <v>0.7142220072816319</v>
+        <v>0.7142220072816334</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1.912043829547575</v>
+        <v>1.912043829547578</v>
       </c>
       <c r="D9">
-        <v>-0.6638684490758788</v>
+        <v>-0.6638684490758776</v>
       </c>
       <c r="E9">
-        <v>0.3990774831625833</v>
+        <v>0.3990774831625856</v>
       </c>
       <c r="F9">
-        <v>0.5858175495450417</v>
+        <v>0.5858175495450458</v>
       </c>
       <c r="G9">
-        <v>1.20074866690557</v>
+        <v>1.200748666905568</v>
       </c>
     </row>
     <row r="10">
@@ -622,16 +622,16 @@
         <v>-1.278817028988705</v>
       </c>
       <c r="D10">
-        <v>1.210141625301078</v>
+        <v>1.210141625301077</v>
       </c>
       <c r="E10">
-        <v>-0.1713518717937325</v>
+        <v>-0.1713518717937348</v>
       </c>
       <c r="F10">
-        <v>-0.1899764284865521</v>
+        <v>-0.1899764284865516</v>
       </c>
       <c r="G10">
-        <v>0.2228856941622443</v>
+        <v>0.2228856941622454</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>1.667641081790975</v>
+        <v>1.667641081790977</v>
       </c>
       <c r="D11">
-        <v>1.132913817558938</v>
+        <v>1.132913817558939</v>
       </c>
       <c r="E11">
-        <v>-0.09507476137952259</v>
+        <v>-0.09507476137952418</v>
       </c>
       <c r="F11">
-        <v>0.3864348196068125</v>
+        <v>0.3864348196068126</v>
       </c>
       <c r="G11">
-        <v>0.2149877736819824</v>
+        <v>0.2149877736819819</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>1.222722466304826</v>
+        <v>1.222722466304828</v>
       </c>
       <c r="D12">
-        <v>0.9987914000326942</v>
+        <v>0.9987914000326941</v>
       </c>
       <c r="E12">
-        <v>-0.4238535452265394</v>
+        <v>-0.4238535452265409</v>
       </c>
       <c r="F12">
-        <v>0.3697189343506209</v>
+        <v>0.3697189343506216</v>
       </c>
       <c r="G12">
-        <v>0.3103708671698949</v>
+        <v>0.3103708671698945</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-2.401432627929075</v>
+        <v>-2.401432627929076</v>
       </c>
       <c r="D13">
-        <v>1.171586023252698</v>
+        <v>1.171586023252696</v>
       </c>
       <c r="E13">
-        <v>-0.693421605840165</v>
+        <v>-0.693421605840168</v>
       </c>
       <c r="F13">
-        <v>-0.6195033135862867</v>
+        <v>-0.6195033135862885</v>
       </c>
       <c r="G13">
-        <v>-0.4672259857895653</v>
+        <v>-0.4672259857895623</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>1.24396909459483</v>
       </c>
       <c r="D14">
-        <v>-1.842372572224384</v>
+        <v>-1.842372572224378</v>
       </c>
       <c r="E14">
-        <v>3.199899888024038</v>
+        <v>3.199899888024042</v>
       </c>
       <c r="F14">
-        <v>1.157007355360619</v>
+        <v>1.157007355360623</v>
       </c>
       <c r="G14">
-        <v>0.9756458983881974</v>
+        <v>0.9756458983881913</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>3.234831999138361</v>
+        <v>3.234831999138365</v>
       </c>
       <c r="D15">
-        <v>2.764180881814499</v>
+        <v>2.764180881814502</v>
       </c>
       <c r="E15">
-        <v>0.524654614980602</v>
+        <v>0.5246546149805977</v>
       </c>
       <c r="F15">
-        <v>0.8456377124973877</v>
+        <v>0.8456377124973855</v>
       </c>
       <c r="G15">
-        <v>-0.2482255805325756</v>
+        <v>-0.2482255805325774</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-2.529941474505148</v>
+        <v>-2.52994147450515</v>
       </c>
       <c r="D16">
-        <v>0.5813032125425004</v>
+        <v>0.5813032125425002</v>
       </c>
       <c r="E16">
-        <v>0.5471764535522319</v>
+        <v>0.5471764535522301</v>
       </c>
       <c r="F16">
-        <v>-0.5334742642671305</v>
+        <v>-0.5334742642671313</v>
       </c>
       <c r="G16">
-        <v>-0.3766232314056837</v>
+        <v>-0.376623231405682</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-1.302251393701335</v>
+        <v>-1.302251393701334</v>
       </c>
       <c r="D17">
-        <v>-0.7381424092129426</v>
+        <v>-0.7381424092129429</v>
       </c>
       <c r="E17">
-        <v>-0.06233195050369527</v>
+        <v>-0.06233195050369519</v>
       </c>
       <c r="F17">
-        <v>-0.1284502080172395</v>
+        <v>-0.1284502080172436</v>
       </c>
       <c r="G17">
-        <v>-1.427493712050419</v>
+        <v>-1.427493712050418</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>1.500887042433253</v>
+        <v>1.500887042433257</v>
       </c>
       <c r="D18">
-        <v>-1.010740246638663</v>
+        <v>-1.010740246638665</v>
       </c>
       <c r="E18">
-        <v>-1.682113901244272</v>
+        <v>-1.68211390124427</v>
       </c>
       <c r="F18">
-        <v>0.03355887879301753</v>
+        <v>0.03355887879301966</v>
       </c>
       <c r="G18">
-        <v>0.5463463461102086</v>
+        <v>0.5463463461102096</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>2.595441843504647</v>
+        <v>2.595441843504651</v>
       </c>
       <c r="D19">
-        <v>1.523465593495278</v>
+        <v>1.523465593495277</v>
       </c>
       <c r="E19">
-        <v>-1.486795681864349</v>
+        <v>-1.486795681864352</v>
       </c>
       <c r="F19">
-        <v>-0.3248493747159388</v>
+        <v>-0.3248493747159414</v>
       </c>
       <c r="G19">
-        <v>-0.589027421682734</v>
+        <v>-0.5890274216827308</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.5341861394730141</v>
+        <v>0.5341861394730161</v>
       </c>
       <c r="D20">
-        <v>-1.833017279863628</v>
+        <v>-1.83301727986363</v>
       </c>
       <c r="E20">
-        <v>-0.730591958569322</v>
+        <v>-0.730591958569319</v>
       </c>
       <c r="F20">
-        <v>0.4630951439145619</v>
+        <v>0.4630951439145635</v>
       </c>
       <c r="G20">
-        <v>0.2274604330644719</v>
+        <v>0.2274604330644703</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.527330492299613</v>
+        <v>0.5273304922996142</v>
       </c>
       <c r="D21">
-        <v>0.9936440681379552</v>
+        <v>0.9936440681379555</v>
       </c>
       <c r="E21">
-        <v>-0.2269976159227721</v>
+        <v>-0.2269976159227734</v>
       </c>
       <c r="F21">
-        <v>1.108907567732033</v>
+        <v>1.108907567732035</v>
       </c>
       <c r="G21">
-        <v>0.8787090231235881</v>
+        <v>0.8787090231235848</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.9869250234509325</v>
+        <v>-0.9869250234509327</v>
       </c>
       <c r="D22">
-        <v>1.08757611384352</v>
+        <v>1.087576113843519</v>
       </c>
       <c r="E22">
-        <v>-0.5310582503529269</v>
+        <v>-0.5310582503529288</v>
       </c>
       <c r="F22">
-        <v>0.5051744894560698</v>
+        <v>0.5051744894560715</v>
       </c>
       <c r="G22">
-        <v>0.5520138573974559</v>
+        <v>0.5520138573974547</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.6728220680073506</v>
+        <v>-0.6728220680073502</v>
       </c>
       <c r="D23">
-        <v>0.4778120974627481</v>
+        <v>0.4778120974627464</v>
       </c>
       <c r="E23">
-        <v>-0.8222342738779542</v>
+        <v>-0.8222342738779551</v>
       </c>
       <c r="F23">
-        <v>0.2003981907316372</v>
+        <v>0.2003981907316389</v>
       </c>
       <c r="G23">
-        <v>0.5336319147116706</v>
+        <v>0.5336319147116705</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.1061288976218555</v>
+        <v>-0.1061288976218552</v>
       </c>
       <c r="D24">
-        <v>1.594503980861734</v>
+        <v>1.594503980861736</v>
       </c>
       <c r="E24">
-        <v>1.076292356666341</v>
+        <v>1.076292356666338</v>
       </c>
       <c r="F24">
-        <v>0.7941941265402278</v>
+        <v>0.7941941265402277</v>
       </c>
       <c r="G24">
-        <v>0.1063681699680192</v>
+        <v>0.1063681699680165</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.3290731029502799</v>
+        <v>-0.3290731029502795</v>
       </c>
       <c r="D25">
-        <v>-0.07925671709169994</v>
+        <v>-0.07925671709170087</v>
       </c>
       <c r="E25">
-        <v>-0.2416921215670482</v>
+        <v>-0.2416921215670479</v>
       </c>
       <c r="F25">
-        <v>-0.1772528537312956</v>
+        <v>-0.1772528537312933</v>
       </c>
       <c r="G25">
-        <v>0.6249148358939908</v>
+        <v>0.6249148358939915</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>1.962647432611473</v>
+        <v>1.962647432611476</v>
       </c>
       <c r="D26">
-        <v>0.6193862322211953</v>
+        <v>0.6193862322211949</v>
       </c>
       <c r="E26">
-        <v>-0.1354496538295061</v>
+        <v>-0.135449653829507</v>
       </c>
       <c r="F26">
-        <v>-1.354385676281982</v>
+        <v>-1.354385676281983</v>
       </c>
       <c r="G26">
-        <v>-0.3521160101539292</v>
+        <v>-0.3521160101539233</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-2.489425001328668</v>
+        <v>-2.489425001328669</v>
       </c>
       <c r="D27">
-        <v>1.343348452757613</v>
+        <v>1.343348452757612</v>
       </c>
       <c r="E27">
-        <v>0.4566384970480769</v>
+        <v>0.4566384970480738</v>
       </c>
       <c r="F27">
-        <v>-0.1677029068289287</v>
+        <v>-0.1677029068289294</v>
       </c>
       <c r="G27">
-        <v>-0.237386596663011</v>
+        <v>-0.2373865966630102</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.2487184825752393</v>
+        <v>-0.2487184825752398</v>
       </c>
       <c r="D28">
         <v>-2.237523030951735</v>
       </c>
       <c r="E28">
-        <v>0.7498622943177721</v>
+        <v>0.7498622943177771</v>
       </c>
       <c r="F28">
-        <v>0.4826598414619614</v>
+        <v>0.4826598414619683</v>
       </c>
       <c r="G28">
-        <v>1.758440858496791</v>
+        <v>1.758440858496789</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-2.588707301629258</v>
+        <v>-2.588707301629259</v>
       </c>
       <c r="D29">
-        <v>1.102605294818626</v>
+        <v>1.102605294818622</v>
       </c>
       <c r="E29">
-        <v>-1.603811808427328</v>
+        <v>-1.603811808427331</v>
       </c>
       <c r="F29">
-        <v>-0.497391537180872</v>
+        <v>-0.4973915371808718</v>
       </c>
       <c r="G29">
-        <v>0.08899763511609143</v>
+        <v>0.08899763511609449</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.531152730595895</v>
+        <v>-0.5311527305958956</v>
       </c>
       <c r="D30">
-        <v>1.011134715304092</v>
+        <v>1.011134715304095</v>
       </c>
       <c r="E30">
-        <v>1.766706613941359</v>
+        <v>1.766706613941357</v>
       </c>
       <c r="F30">
         <v>0.7002438790838748</v>
       </c>
       <c r="G30">
-        <v>-0.01259917518581081</v>
+        <v>-0.01259917518581399</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.628626687720408</v>
+        <v>-0.6286266877204071</v>
       </c>
       <c r="D31">
-        <v>1.326386479205079</v>
+        <v>1.326386479205078</v>
       </c>
       <c r="E31">
-        <v>-0.7590954959787889</v>
+        <v>-0.7590954959787921</v>
       </c>
       <c r="F31">
-        <v>0.127322367456259</v>
+        <v>0.1273223674562568</v>
       </c>
       <c r="G31">
-        <v>-0.5141861293788352</v>
+        <v>-0.5141861293788346</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>-1.312930420219274</v>
+        <v>-1.312930420219275</v>
       </c>
       <c r="D32">
-        <v>0.6041106045204595</v>
+        <v>0.6041106045204598</v>
       </c>
       <c r="E32">
-        <v>0.5414959860393573</v>
+        <v>0.5414959860393559</v>
       </c>
       <c r="F32">
-        <v>0.06652900074041028</v>
+        <v>0.06652900074040999</v>
       </c>
       <c r="G32">
-        <v>-0.1415797606230067</v>
+        <v>-0.141579760623007</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>3.828853696430335</v>
+        <v>3.82885369643034</v>
       </c>
       <c r="D33">
-        <v>-0.4603776744738209</v>
+        <v>-0.4603776744738223</v>
       </c>
       <c r="E33">
-        <v>-1.373139836304472</v>
+        <v>-1.37313983630447</v>
       </c>
       <c r="F33">
-        <v>-0.982330674931196</v>
+        <v>-0.9823306749311933</v>
       </c>
       <c r="G33">
-        <v>0.8906394633499524</v>
+        <v>0.8906394633499572</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>-1.372373196888317</v>
+        <v>-1.372373196888318</v>
       </c>
       <c r="D34">
-        <v>-0.4405384892898409</v>
+        <v>-0.4405384892898428</v>
       </c>
       <c r="E34">
-        <v>-0.609845812023194</v>
+        <v>-0.6098458120231935</v>
       </c>
       <c r="F34">
-        <v>-0.3407832442816967</v>
+        <v>-0.3407832442816943</v>
       </c>
       <c r="G34">
-        <v>0.6048267201797658</v>
+        <v>0.6048267201797672</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.06024653638840868</v>
+        <v>-0.06024653638840675</v>
       </c>
       <c r="D35">
-        <v>-2.633961021845875</v>
+        <v>-2.633961021845874</v>
       </c>
       <c r="E35">
-        <v>0.4491238048809613</v>
+        <v>0.4491238048809642</v>
       </c>
       <c r="F35">
-        <v>0.4558745738592471</v>
+        <v>0.4558745738592407</v>
       </c>
       <c r="G35">
-        <v>-2.290703494656376</v>
+        <v>-2.290703494656378</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.07450172633237669</v>
+        <v>0.07450172633237688</v>
       </c>
       <c r="D36">
-        <v>-0.1168778922386278</v>
+        <v>-0.1168778922386267</v>
       </c>
       <c r="E36">
-        <v>0.9539879787974289</v>
+        <v>0.9539879787974292</v>
       </c>
       <c r="F36">
-        <v>-0.2070156999340617</v>
+        <v>-0.2070156999340601</v>
       </c>
       <c r="G36">
-        <v>0.4066078073399221</v>
+        <v>0.4066078073399225</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>1.658736825799217</v>
+        <v>1.658736825799218</v>
       </c>
       <c r="D37">
-        <v>-1.42107798105008</v>
+        <v>-1.421077981050076</v>
       </c>
       <c r="E37">
-        <v>2.585313780868762</v>
+        <v>2.585313780868766</v>
       </c>
       <c r="F37">
-        <v>0.3630062668260979</v>
+        <v>0.363006266826101</v>
       </c>
       <c r="G37">
-        <v>0.7454527743233736</v>
+        <v>0.7454527743233706</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>-1.618848481795293</v>
+        <v>-1.618848481795294</v>
       </c>
       <c r="D38">
-        <v>-0.5180206791645179</v>
+        <v>-0.5180206791645201</v>
       </c>
       <c r="E38">
-        <v>-0.3375426695066889</v>
+        <v>-0.3375426695066888</v>
       </c>
       <c r="F38">
         <v>-1.725343258682095</v>
       </c>
       <c r="G38">
-        <v>-0.1888783425249803</v>
+        <v>-0.1888783425249738</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.4451581446607139</v>
+        <v>-0.4451581446607135</v>
       </c>
       <c r="D39">
-        <v>0.04091444887547955</v>
+        <v>0.04091444887548062</v>
       </c>
       <c r="E39">
-        <v>0.7281358471716235</v>
+        <v>0.7281358471716231</v>
       </c>
       <c r="F39">
-        <v>0.3374055667517606</v>
+        <v>0.3374055667517598</v>
       </c>
       <c r="G39">
-        <v>-0.3576661092948734</v>
+        <v>-0.3576661092948749</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.2553380248312293</v>
+        <v>-0.2553380248312295</v>
       </c>
       <c r="D40">
-        <v>0.6157863080296822</v>
+        <v>0.6157863080296853</v>
       </c>
       <c r="E40">
-        <v>1.917554540656359</v>
+        <v>1.917554540656358</v>
       </c>
       <c r="F40">
-        <v>0.8164632614661729</v>
+        <v>0.8164632614661727</v>
       </c>
       <c r="G40">
-        <v>-0.1436519220537052</v>
+        <v>-0.1436519220537088</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.2541022468668842</v>
+        <v>-0.2541022468668835</v>
       </c>
       <c r="D41">
-        <v>0.5688336070790657</v>
+        <v>0.5688336070790643</v>
       </c>
       <c r="E41">
-        <v>-0.7707633911890995</v>
+        <v>-0.7707633911891006</v>
       </c>
       <c r="F41">
-        <v>0.05046451455117425</v>
+        <v>0.05046451455117654</v>
       </c>
       <c r="G41">
-        <v>0.7510182917406174</v>
+        <v>0.7510182917406178</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>-0.9431273317455122</v>
+        <v>-0.943127331745513</v>
       </c>
       <c r="D42">
         <v>-1.752157459868451</v>
       </c>
       <c r="E42">
-        <v>0.3380390021941724</v>
+        <v>0.3380390021941758</v>
       </c>
       <c r="F42">
-        <v>0.2658927787405966</v>
+        <v>0.265892778740602</v>
       </c>
       <c r="G42">
-        <v>1.372975313611435</v>
+        <v>1.372975313611433</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.9605558091027534</v>
+        <v>-0.9605558091027551</v>
       </c>
       <c r="D43">
-        <v>-0.5531257604944111</v>
+        <v>-0.5531257604944084</v>
       </c>
       <c r="E43">
         <v>2.473811902447768</v>
       </c>
       <c r="F43">
-        <v>-0.7353375797082408</v>
+        <v>-0.7353375797082404</v>
       </c>
       <c r="G43">
-        <v>-0.06987051569524944</v>
+        <v>-0.06987051569524794</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.5797154321736142</v>
+        <v>-0.5797154321736138</v>
       </c>
       <c r="D44">
-        <v>-3.034878461031429</v>
+        <v>-3.03487846103143</v>
       </c>
       <c r="E44">
-        <v>-0.4355379639792625</v>
+        <v>-0.4355379639792576</v>
       </c>
       <c r="F44">
-        <v>-0.7644182981286468</v>
+        <v>-0.7644182981286451</v>
       </c>
       <c r="G44">
-        <v>0.09510616692346315</v>
+        <v>0.09510616692346519</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>-1.759512769045633</v>
+        <v>-1.759512769045634</v>
       </c>
       <c r="D45">
-        <v>0.3447352151838566</v>
+        <v>0.3447352151838559</v>
       </c>
       <c r="E45">
-        <v>0.005893159397017993</v>
+        <v>0.005893159397017109</v>
       </c>
       <c r="F45">
-        <v>0.1234814791386059</v>
+        <v>0.1234814791386078</v>
       </c>
       <c r="G45">
-        <v>0.4984161015528972</v>
+        <v>0.4984161015528968</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>1.394872185388936</v>
+        <v>1.394872185388937</v>
       </c>
       <c r="D46">
-        <v>0.7811475882812468</v>
+        <v>0.7811475882812499</v>
       </c>
       <c r="E46">
         <v>1.558243602136459</v>
       </c>
       <c r="F46">
-        <v>0.4830241692005537</v>
+        <v>0.4830241692005545</v>
       </c>
       <c r="G46">
-        <v>0.3104026356479805</v>
+        <v>0.3104026356479785</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.3354468523601978</v>
+        <v>-0.3354468523601962</v>
       </c>
       <c r="D47">
-        <v>-0.05329855208875035</v>
+        <v>-0.05329855208875278</v>
       </c>
       <c r="E47">
-        <v>-1.625518063010355</v>
+        <v>-1.625518063010356</v>
       </c>
       <c r="F47">
-        <v>0.5875451044793258</v>
+        <v>0.5875451044793261</v>
       </c>
       <c r="G47">
-        <v>0.03608747082288128</v>
+        <v>0.03608747082288</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.9662416305735362</v>
+        <v>-0.9662416305735366</v>
       </c>
       <c r="D48">
-        <v>-1.787545323295043</v>
+        <v>-1.787545323295045</v>
       </c>
       <c r="E48">
-        <v>-0.539207092827053</v>
+        <v>-0.5392070928270494</v>
       </c>
       <c r="F48">
-        <v>-0.2293478014195305</v>
+        <v>-0.2293478014195239</v>
       </c>
       <c r="G48">
-        <v>1.802209493742844</v>
+        <v>1.802209493742845</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.1428814306601149</v>
+        <v>-0.142881430660114</v>
       </c>
       <c r="D49">
-        <v>0.1773315067788689</v>
+        <v>0.1773315067788678</v>
       </c>
       <c r="E49">
-        <v>-0.3858412174845316</v>
+        <v>-0.3858412174845322</v>
       </c>
       <c r="F49">
-        <v>-0.5150195038402626</v>
+        <v>-0.5150195038402625</v>
       </c>
       <c r="G49">
-        <v>-0.0002416337272016292</v>
+        <v>-0.0002416337271992364</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-1.103012429580608</v>
+        <v>-1.103012429580609</v>
       </c>
       <c r="D50">
         <v>-0.1089262745327964</v>
       </c>
       <c r="E50">
-        <v>0.9031266734572894</v>
+        <v>0.9031266734572891</v>
       </c>
       <c r="F50">
-        <v>-1.366048721887001</v>
+        <v>-1.366048721887002</v>
       </c>
       <c r="G50">
-        <v>-0.1947096911751048</v>
+        <v>-0.1947096911750998</v>
       </c>
     </row>
     <row r="51">
@@ -1729,16 +1729,16 @@
         <v>-1.405452112130976</v>
       </c>
       <c r="D51">
-        <v>0.9748966146614338</v>
+        <v>0.9748966146614322</v>
       </c>
       <c r="E51">
-        <v>-0.7081310436158413</v>
+        <v>-0.7081310436158431</v>
       </c>
       <c r="F51">
-        <v>0.1150867359885369</v>
+        <v>0.1150867359885393</v>
       </c>
       <c r="G51">
-        <v>0.7099131964855241</v>
+        <v>0.7099131964855244</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.34969202730846</v>
+        <v>0.3496920273084612</v>
       </c>
       <c r="D52">
-        <v>-2.192853123822523</v>
+        <v>-2.192853123822524</v>
       </c>
       <c r="E52">
-        <v>-0.224558266089023</v>
+        <v>-0.224558266089019</v>
       </c>
       <c r="F52">
-        <v>-0.2855625222506107</v>
+        <v>-0.285562522250608</v>
       </c>
       <c r="G52">
-        <v>0.5471915505837862</v>
+        <v>0.547191550583787</v>
       </c>
     </row>
     <row r="53">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="C53">
-        <v>1.188914629355684</v>
+        <v>1.188914629355687</v>
       </c>
       <c r="D53">
-        <v>-0.9201332634333111</v>
+        <v>-0.9201332634333097</v>
       </c>
       <c r="E53">
-        <v>0.3072699765638816</v>
+        <v>0.3072699765638826</v>
       </c>
       <c r="F53">
-        <v>0.1775770303228832</v>
+        <v>0.1775770303228786</v>
       </c>
       <c r="G53">
         <v>-1.478112031187373</v>
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.4944576428541271</v>
+        <v>-0.4944576428541265</v>
       </c>
       <c r="D54">
         <v>1.098114810424881</v>
       </c>
       <c r="E54">
-        <v>-0.02747466201696049</v>
+        <v>-0.02747466201696291</v>
       </c>
       <c r="F54">
-        <v>0.3966973712795686</v>
+        <v>0.3966973712795667</v>
       </c>
       <c r="G54">
-        <v>-0.4919329367417746</v>
+        <v>-0.4919329367417754</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>2.253578252221947</v>
+        <v>2.253578252221951</v>
       </c>
       <c r="D55">
-        <v>-1.16141744465751</v>
+        <v>-1.161417444657509</v>
       </c>
       <c r="E55">
-        <v>0.2088615821393515</v>
+        <v>0.2088615821393533</v>
       </c>
       <c r="F55">
-        <v>0.6112380301997746</v>
+        <v>0.6112380301997715</v>
       </c>
       <c r="G55">
-        <v>-1.025126439799548</v>
+        <v>-1.02512643979955</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.7799836928244318</v>
+        <v>-0.7799836928244315</v>
       </c>
       <c r="D56">
-        <v>-1.311134193864802</v>
+        <v>-1.311134193864804</v>
       </c>
       <c r="E56">
-        <v>-1.107046808525096</v>
+        <v>-1.107046808525094</v>
       </c>
       <c r="F56">
-        <v>0.9984300527482153</v>
+        <v>0.9984300527482188</v>
       </c>
       <c r="G56">
-        <v>0.8813691242799272</v>
+        <v>0.8813691242799234</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.4616807592226528</v>
+        <v>-0.4616807592226515</v>
       </c>
       <c r="D57">
-        <v>-0.6631756539827213</v>
+        <v>-0.6631756539827209</v>
       </c>
       <c r="E57">
-        <v>-0.3788861836291705</v>
+        <v>-0.3788861836291698</v>
       </c>
       <c r="F57">
-        <v>1.958723616372587</v>
+        <v>1.958723616372586</v>
       </c>
       <c r="G57">
-        <v>-0.3120215612862156</v>
+        <v>-0.3120215612862226</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>1.949800249652955</v>
+        <v>1.949800249652958</v>
       </c>
       <c r="D58">
-        <v>1.834680008777199</v>
+        <v>1.8346800087772</v>
       </c>
       <c r="E58">
-        <v>-0.4274171821316258</v>
+        <v>-0.4274171821316288</v>
       </c>
       <c r="F58">
-        <v>1.143510706802039</v>
+        <v>1.143510706802037</v>
       </c>
       <c r="G58">
-        <v>-0.3299495038960749</v>
+        <v>-0.3299495038960776</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>1.371566567947018</v>
+        <v>1.37156656794702</v>
       </c>
       <c r="D59">
-        <v>0.9129598900587499</v>
+        <v>0.912959890058749</v>
       </c>
       <c r="E59">
-        <v>-0.5305105674437105</v>
+        <v>-0.5305105674437119</v>
       </c>
       <c r="F59">
-        <v>-1.170231963723533</v>
+        <v>-1.170231963723535</v>
       </c>
       <c r="G59">
-        <v>-0.1773150402394383</v>
+        <v>-0.1773150402394328</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.06350481918872704</v>
+        <v>0.06350481918872813</v>
       </c>
       <c r="D60">
-        <v>-1.774715542564341</v>
+        <v>-1.774715542564343</v>
       </c>
       <c r="E60">
-        <v>-0.6192907902211869</v>
+        <v>-0.6192907902211838</v>
       </c>
       <c r="F60">
-        <v>0.1225794992935996</v>
+        <v>0.1225794992936028</v>
       </c>
       <c r="G60">
-        <v>0.7604062601437563</v>
+        <v>0.7604062601437559</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-2.005742041936403</v>
+        <v>-2.005742041936404</v>
       </c>
       <c r="D61">
-        <v>1.701767264482169</v>
+        <v>1.70176726448217</v>
       </c>
       <c r="E61">
-        <v>0.5943338986247951</v>
+        <v>0.5943338986247915</v>
       </c>
       <c r="F61">
-        <v>-0.1232143029462378</v>
+        <v>-0.123214302946239</v>
       </c>
       <c r="G61">
-        <v>-0.2709110415418226</v>
+        <v>-0.2709110415418223</v>
       </c>
     </row>
     <row r="62">
@@ -2026,16 +2026,16 @@
         <v>-1.674109526489327</v>
       </c>
       <c r="D62">
-        <v>0.6867595148344841</v>
+        <v>0.6867595148344825</v>
       </c>
       <c r="E62">
-        <v>-0.4812417142040775</v>
+        <v>-0.4812417142040793</v>
       </c>
       <c r="F62">
-        <v>-0.09712905640773148</v>
+        <v>-0.09712905640773115</v>
       </c>
       <c r="G62">
-        <v>0.09242031561843575</v>
+        <v>0.09242031561843655</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>-1.166311921148971</v>
+        <v>-1.166311921148972</v>
       </c>
       <c r="D63">
-        <v>1.05988518417219</v>
+        <v>1.059885184172189</v>
       </c>
       <c r="E63">
-        <v>-0.1664294991366839</v>
+        <v>-0.1664294991366859</v>
       </c>
       <c r="F63">
-        <v>0.2075824723214449</v>
+        <v>0.2075824723214458</v>
       </c>
       <c r="G63">
-        <v>0.3158014456947664</v>
+        <v>0.315801445694766</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.04578202963086239</v>
+        <v>0.04578202963086297</v>
       </c>
       <c r="D64">
-        <v>-0.7347295855857269</v>
+        <v>-0.7347295855857268</v>
       </c>
       <c r="E64">
-        <v>-0.117282782351232</v>
+        <v>-0.1172827823512302</v>
       </c>
       <c r="F64">
-        <v>1.130358486798416</v>
+        <v>1.13035848679842</v>
       </c>
       <c r="G64">
-        <v>1.197025668422691</v>
+        <v>1.197025668422687</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>-0.5581566447401484</v>
+        <v>-0.5581566447401478</v>
       </c>
       <c r="D65">
-        <v>0.1298784579491759</v>
+        <v>0.1298784579491725</v>
       </c>
       <c r="E65">
-        <v>-1.703671542928324</v>
+        <v>-1.703671542928323</v>
       </c>
       <c r="F65">
-        <v>-0.07082447764854469</v>
+        <v>-0.07082447764854033</v>
       </c>
       <c r="G65">
-        <v>1.344692241396448</v>
+        <v>1.344692241396449</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>1.20600274800383</v>
+        <v>1.206002748003832</v>
       </c>
       <c r="D66">
-        <v>0.1730407448255806</v>
+        <v>0.1730407448255793</v>
       </c>
       <c r="E66">
         <v>-0.8119105819618302</v>
       </c>
       <c r="F66">
-        <v>-0.5609639251545372</v>
+        <v>-0.560963925154536</v>
       </c>
       <c r="G66">
-        <v>0.3619636057839109</v>
+        <v>0.3619636057839138</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.1625831628361281</v>
+        <v>0.1625831628361291</v>
       </c>
       <c r="D67">
-        <v>-0.01076127237219109</v>
+        <v>-0.01076127237219182</v>
       </c>
       <c r="E67">
-        <v>-0.5069938712875104</v>
+        <v>-0.5069938712875099</v>
       </c>
       <c r="F67">
-        <v>0.6261406911205885</v>
+        <v>0.6261406911205913</v>
       </c>
       <c r="G67">
-        <v>0.8830116585802877</v>
+        <v>0.8830116585802856</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.1962487977882142</v>
+        <v>0.1962487977882144</v>
       </c>
       <c r="D68">
-        <v>-1.501278336770894</v>
+        <v>-1.501278336770892</v>
       </c>
       <c r="E68">
-        <v>1.689462049441044</v>
+        <v>1.689462049441047</v>
       </c>
       <c r="F68">
-        <v>-0.5984216674963321</v>
+        <v>-0.5984216674963307</v>
       </c>
       <c r="G68">
-        <v>0.1489847712193546</v>
+        <v>0.1489847712193557</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.1678372183253341</v>
+        <v>0.1678372183253347</v>
       </c>
       <c r="D69">
-        <v>0.0260160694986564</v>
+        <v>0.02601606949865784</v>
       </c>
       <c r="E69">
-        <v>0.8196194650572264</v>
+        <v>0.8196194650572265</v>
       </c>
       <c r="F69">
-        <v>0.3686674963269247</v>
+        <v>0.3686674963269248</v>
       </c>
       <c r="G69">
-        <v>0.025582449948503</v>
+        <v>0.02558244994850159</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.6004725484136988</v>
+        <v>-0.600472548413696</v>
       </c>
       <c r="D70">
-        <v>-1.980397687627352</v>
+        <v>-1.980397687627355</v>
       </c>
       <c r="E70">
-        <v>-2.344561213724267</v>
+        <v>-2.344561213724266</v>
       </c>
       <c r="F70">
-        <v>1.388988755521925</v>
+        <v>1.388988755521922</v>
       </c>
       <c r="G70">
-        <v>-1.373436106439237</v>
+        <v>-1.373436106439241</v>
       </c>
     </row>
     <row r="71">
@@ -2269,16 +2269,16 @@
         <v>-1.450818341256115</v>
       </c>
       <c r="D71">
-        <v>1.068418802182659</v>
+        <v>1.068418802182658</v>
       </c>
       <c r="E71">
-        <v>-0.7484291698173761</v>
+        <v>-0.7484291698173783</v>
       </c>
       <c r="F71">
-        <v>-0.2504790375445143</v>
+        <v>-0.2504790375445138</v>
       </c>
       <c r="G71">
-        <v>0.1571395975102184</v>
+        <v>0.1571395975102202</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.04221854727543767</v>
+        <v>0.04221854727543864</v>
       </c>
       <c r="D72">
-        <v>-1.249443349291669</v>
+        <v>-1.249443349291672</v>
       </c>
       <c r="E72">
-        <v>-1.025159129791002</v>
+        <v>-1.025159129791</v>
       </c>
       <c r="F72">
-        <v>-2.174000061632504</v>
+        <v>-2.174000061632503</v>
       </c>
       <c r="G72">
-        <v>0.2614051992336219</v>
+        <v>0.2614051992336304</v>
       </c>
     </row>
     <row r="73">
@@ -2323,16 +2323,16 @@
         <v>-1.223322755949776</v>
       </c>
       <c r="D73">
-        <v>-0.3259616307555822</v>
+        <v>-0.3259616307555832</v>
       </c>
       <c r="E73">
         <v>0.03631425991059987</v>
       </c>
       <c r="F73">
-        <v>-0.8145314246106603</v>
+        <v>-0.8145314246106605</v>
       </c>
       <c r="G73">
-        <v>-0.190523998562379</v>
+        <v>-0.1905239985623761</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-1.235173817549427</v>
+        <v>-1.235173817549428</v>
       </c>
       <c r="D74">
-        <v>0.4818472533230813</v>
+        <v>0.4818472533230814</v>
       </c>
       <c r="E74">
-        <v>0.7814645811559481</v>
+        <v>0.7814645811559464</v>
       </c>
       <c r="F74">
-        <v>-1.373804442622119</v>
+        <v>-1.373804442622123</v>
       </c>
       <c r="G74">
-        <v>-1.070359736841803</v>
+        <v>-1.070359736841798</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>3.605465289960752</v>
+        <v>3.605465289960756</v>
       </c>
       <c r="D75">
-        <v>1.847778376877704</v>
+        <v>1.84777837687771</v>
       </c>
       <c r="E75">
-        <v>2.456075323679062</v>
+        <v>2.45607532367906</v>
       </c>
       <c r="F75">
-        <v>0.5604085200212445</v>
+        <v>0.5604085200212412</v>
       </c>
       <c r="G75">
-        <v>-0.7538647954840214</v>
+        <v>-0.753864795484023</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>0.8085651337891432</v>
+        <v>0.8085651337891449</v>
       </c>
       <c r="D76">
         <v>1.881287940442743</v>
       </c>
       <c r="E76">
-        <v>0.05019223547368293</v>
+        <v>0.05019223547367982</v>
       </c>
       <c r="F76">
-        <v>0.2126212383054064</v>
+        <v>0.2126212383054055</v>
       </c>
       <c r="G76">
-        <v>-0.06795463724803812</v>
+        <v>-0.06795463724803796</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.3580895515760841</v>
+        <v>0.358089551576086</v>
       </c>
       <c r="D77">
-        <v>0.0759706371841387</v>
+        <v>0.07597063718413909</v>
       </c>
       <c r="E77">
-        <v>-0.3250827554917104</v>
+        <v>-0.3250827554917112</v>
       </c>
       <c r="F77">
-        <v>1.217907792495266</v>
+        <v>1.217907792495263</v>
       </c>
       <c r="G77">
-        <v>-0.8251411038040547</v>
+        <v>-0.8251411038040585</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>-0.8123421154952811</v>
+        <v>-0.8123421154952789</v>
       </c>
       <c r="D78">
-        <v>-1.277648573156481</v>
+        <v>-1.277648573156482</v>
       </c>
       <c r="E78">
-        <v>-0.6508530644373114</v>
+        <v>-0.6508530644373113</v>
       </c>
       <c r="F78">
-        <v>2.087430430561155</v>
+        <v>2.087430430561148</v>
       </c>
       <c r="G78">
-        <v>-2.480575610080246</v>
+        <v>-2.480575610080254</v>
       </c>
     </row>
     <row r="79">
@@ -2485,16 +2485,16 @@
         <v>-1.159792376240714</v>
       </c>
       <c r="D79">
-        <v>2.462605465971649</v>
+        <v>2.462605465971646</v>
       </c>
       <c r="E79">
-        <v>-1.853128461791018</v>
+        <v>-1.853128461791022</v>
       </c>
       <c r="F79">
-        <v>-0.28362320684547</v>
+        <v>-0.2836232068454705</v>
       </c>
       <c r="G79">
-        <v>0.04030538301041579</v>
+        <v>0.04030538301041842</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>1.300397791599024</v>
+        <v>1.300397791599026</v>
       </c>
       <c r="D80">
-        <v>1.996464285452074</v>
+        <v>1.996464285452076</v>
       </c>
       <c r="E80">
-        <v>0.7068042371547382</v>
+        <v>0.7068042371547349</v>
       </c>
       <c r="F80">
-        <v>0.1302991929225368</v>
+        <v>0.1302991929225354</v>
       </c>
       <c r="G80">
-        <v>-0.1604545921245982</v>
+        <v>-0.1604545921245979</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>1.470363794322061</v>
+        <v>1.470363794322064</v>
       </c>
       <c r="D81">
         <v>-1.096915017148692</v>
       </c>
       <c r="E81">
-        <v>0.136484834757732</v>
+        <v>0.1364848347577335</v>
       </c>
       <c r="F81">
-        <v>0.1445176663013248</v>
+        <v>0.1445176663013222</v>
       </c>
       <c r="G81">
-        <v>-0.9160895748699958</v>
+        <v>-0.916089574869996</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.2356831719981768</v>
+        <v>0.2356831719981778</v>
       </c>
       <c r="D82">
-        <v>-1.551721211774498</v>
+        <v>-1.551721211774501</v>
       </c>
       <c r="E82">
-        <v>-0.1033412912143242</v>
+        <v>-0.103341291214322</v>
       </c>
       <c r="F82">
-        <v>-3.589858869443574</v>
+        <v>-3.589858869443576</v>
       </c>
       <c r="G82">
-        <v>-0.874565272984001</v>
+        <v>-0.8745652729839875</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>1.725685184704126</v>
+        <v>1.72568518470413</v>
       </c>
       <c r="D83">
-        <v>-1.500043131574791</v>
+        <v>-1.500043131574792</v>
       </c>
       <c r="E83">
-        <v>-1.363915213382318</v>
+        <v>-1.363915213382316</v>
       </c>
       <c r="F83">
-        <v>1.174746926794026</v>
+        <v>1.174746926794022</v>
       </c>
       <c r="G83">
-        <v>-1.247284264627656</v>
+        <v>-1.24728426462766</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>1.189976391279916</v>
+        <v>1.189976391279918</v>
       </c>
       <c r="D84">
-        <v>0.6573306868568827</v>
+        <v>0.6573306868568819</v>
       </c>
       <c r="E84">
-        <v>-0.6123736833542011</v>
+        <v>-0.6123736833542019</v>
       </c>
       <c r="F84">
-        <v>0.2058774129431074</v>
+        <v>0.2058774129431086</v>
       </c>
       <c r="G84">
-        <v>0.4767732496506911</v>
+        <v>0.4767732496506912</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>-1.212417599873018</v>
+        <v>-1.212417599873017</v>
       </c>
       <c r="D85">
-        <v>0.05391781063661785</v>
+        <v>0.05391781063661572</v>
       </c>
       <c r="E85">
         <v>-1.224788065637571</v>
       </c>
       <c r="F85">
-        <v>0.9534452888228911</v>
+        <v>0.9534452888228946</v>
       </c>
       <c r="G85">
-        <v>0.9765484644404872</v>
+        <v>0.9765484644404842</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>-1.42977653324684</v>
+        <v>-1.429776533246839</v>
       </c>
       <c r="D86">
-        <v>-1.927045806296041</v>
+        <v>-1.927045806296043</v>
       </c>
       <c r="E86">
-        <v>-0.6557543949331405</v>
+        <v>-0.6557543949331385</v>
       </c>
       <c r="F86">
-        <v>1.091572165527567</v>
+        <v>1.091572165527565</v>
       </c>
       <c r="G86">
-        <v>-1.030117325432163</v>
+        <v>-1.030117325432168</v>
       </c>
     </row>
     <row r="87">
@@ -2701,16 +2701,16 @@
         <v>-1.307420061342078</v>
       </c>
       <c r="D87">
-        <v>1.409107880706578</v>
+        <v>1.409107880706577</v>
       </c>
       <c r="E87">
-        <v>0.1603136093136014</v>
+        <v>0.1603136093135983</v>
       </c>
       <c r="F87">
-        <v>-0.6564112806575719</v>
+        <v>-0.6564112806575739</v>
       </c>
       <c r="G87">
-        <v>-0.5950930891010228</v>
+        <v>-0.5950930891010197</v>
       </c>
     </row>
     <row r="88">
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.3335727604480906</v>
+        <v>0.3335727604480915</v>
       </c>
       <c r="D88">
-        <v>-1.824766492995338</v>
+        <v>-1.824766492995341</v>
       </c>
       <c r="E88">
-        <v>-1.424427910617275</v>
+        <v>-1.424427910617271</v>
       </c>
       <c r="F88">
-        <v>0.09754281376188517</v>
+        <v>0.09754281376189233</v>
       </c>
       <c r="G88">
         <v>2.024414171061748</v>
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.02016228132551776</v>
+        <v>0.02016228132551838</v>
       </c>
       <c r="D89">
-        <v>0.5431586958108855</v>
+        <v>0.5431586958108859</v>
       </c>
       <c r="E89">
-        <v>0.2567260028089514</v>
+        <v>0.2567260028089506</v>
       </c>
       <c r="F89">
-        <v>0.5142044900272501</v>
+        <v>0.5142044900272513</v>
       </c>
       <c r="G89">
-        <v>0.3786073485770442</v>
+        <v>0.3786073485770426</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>1.135480229099371</v>
+        <v>1.135480229099373</v>
       </c>
       <c r="D90">
         <v>2.171435094846276</v>
       </c>
       <c r="E90">
-        <v>-0.148102348280169</v>
+        <v>-0.1481023482801725</v>
       </c>
       <c r="F90">
-        <v>1.031959549939736</v>
+        <v>1.031959549939735</v>
       </c>
       <c r="G90">
-        <v>0.2048096743725274</v>
+        <v>0.2048096743725247</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.05675605867493502</v>
+        <v>0.05675605867493566</v>
       </c>
       <c r="D91">
-        <v>0.05559158633577392</v>
+        <v>0.05559158633577443</v>
       </c>
       <c r="E91">
-        <v>0.994472154906144</v>
+        <v>0.9944721549061435</v>
       </c>
       <c r="F91">
-        <v>-2.052319120273848</v>
+        <v>-2.052319120273851</v>
       </c>
       <c r="G91">
-        <v>-1.213248523829646</v>
+        <v>-1.213248523829639</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.118374542512975</v>
+        <v>0.118374542512976</v>
       </c>
       <c r="D92">
-        <v>0.8808248428670798</v>
+        <v>0.8808248428670811</v>
       </c>
       <c r="E92">
-        <v>0.4084515510036082</v>
+        <v>0.4084515510036064</v>
       </c>
       <c r="F92">
-        <v>1.147021832977535</v>
+        <v>1.147021832977534</v>
       </c>
       <c r="G92">
-        <v>-0.2946190001820742</v>
+        <v>-0.294619000182078</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>2.064644730358685</v>
+        <v>2.064644730358687</v>
       </c>
       <c r="D93">
         <v>-0.8636502911962221</v>
       </c>
       <c r="E93">
-        <v>0.09214032775174057</v>
+        <v>0.09214032775174238</v>
       </c>
       <c r="F93">
-        <v>-0.9410074504478267</v>
+        <v>-0.9410074504478266</v>
       </c>
       <c r="G93">
-        <v>0.003870402407539718</v>
+        <v>0.003870402407543549</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.1922593490049951</v>
+        <v>-0.192259349004995</v>
       </c>
       <c r="D94">
-        <v>0.8408221565360854</v>
+        <v>0.8408221565360868</v>
       </c>
       <c r="E94">
-        <v>1.121497820857642</v>
+        <v>1.121497820857641</v>
       </c>
       <c r="F94">
-        <v>-0.1860771142637815</v>
+        <v>-0.1860771142637824</v>
       </c>
       <c r="G94">
-        <v>-0.2229376197970495</v>
+        <v>-0.2229376197970488</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-0.2357579669918149</v>
+        <v>-0.235757966991814</v>
       </c>
       <c r="D95">
-        <v>1.49086428766785</v>
+        <v>1.490864287667849</v>
       </c>
       <c r="E95">
-        <v>-0.4821359267315979</v>
+        <v>-0.4821359267316007</v>
       </c>
       <c r="F95">
-        <v>-0.2620146606583423</v>
+        <v>-0.2620146606583439</v>
       </c>
       <c r="G95">
-        <v>-0.3237550824523368</v>
+        <v>-0.3237550824523349</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.6570907692225358</v>
+        <v>-0.6570907692225348</v>
       </c>
       <c r="D96">
-        <v>0.1076600119375851</v>
+        <v>0.1076600119375853</v>
       </c>
       <c r="E96">
-        <v>-0.2367381396902606</v>
+        <v>-0.2367381396902616</v>
       </c>
       <c r="F96">
-        <v>1.13798531061168</v>
+        <v>1.137985310611677</v>
       </c>
       <c r="G96">
-        <v>-0.9983832023963131</v>
+        <v>-0.9983832023963168</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>3.882814846273904</v>
+        <v>3.882814846273908</v>
       </c>
       <c r="D97">
         <v>0.7223766080537563</v>
       </c>
       <c r="E97">
-        <v>-0.8141741651120749</v>
+        <v>-0.814174165112075</v>
       </c>
       <c r="F97">
-        <v>0.087206876897844</v>
+        <v>0.08720687689784584</v>
       </c>
       <c r="G97">
-        <v>0.8192581139565084</v>
+        <v>0.8192581139565094</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-1.388870331320305</v>
+        <v>-1.388870331320306</v>
       </c>
       <c r="D98">
-        <v>0.4170153020503075</v>
+        <v>0.4170153020503076</v>
       </c>
       <c r="E98">
-        <v>0.804351538363989</v>
+        <v>0.8043515383639877</v>
       </c>
       <c r="F98">
-        <v>-1.103094582610138</v>
+        <v>-1.10309458261014</v>
       </c>
       <c r="G98">
-        <v>-0.4702623078884619</v>
+        <v>-0.470262307888458</v>
       </c>
     </row>
     <row r="99">
@@ -3025,16 +3025,16 @@
         <v>-1.288213399366346</v>
       </c>
       <c r="D99">
-        <v>0.7083339011147384</v>
+        <v>0.7083339011147379</v>
       </c>
       <c r="E99">
-        <v>0.0003148433072986736</v>
+        <v>0.0003148433072968637</v>
       </c>
       <c r="F99">
-        <v>-0.07470701475020887</v>
+        <v>-0.07470701475020963</v>
       </c>
       <c r="G99">
-        <v>-0.2539144558469776</v>
+        <v>-0.253914455846977</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.7216851385888122</v>
+        <v>-0.7216851385888114</v>
       </c>
       <c r="D100">
-        <v>-0.08625295864164957</v>
+        <v>-0.08625295864165292</v>
       </c>
       <c r="E100">
         <v>-1.756982068352321</v>
       </c>
       <c r="F100">
-        <v>-0.4332911268899367</v>
+        <v>-0.4332911268899355</v>
       </c>
       <c r="G100">
-        <v>0.3217809692180539</v>
+        <v>0.3217809692180563</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>-0.1269092211572329</v>
+        <v>-0.1269092211572307</v>
       </c>
       <c r="D101">
-        <v>-0.718491639749107</v>
+        <v>-0.7184916397491071</v>
       </c>
       <c r="E101">
-        <v>-0.8018590078877842</v>
+        <v>-0.8018590078877836</v>
       </c>
       <c r="F101">
-        <v>2.354949524748258</v>
+        <v>2.354949524748255</v>
       </c>
       <c r="G101">
-        <v>-0.9793692007857905</v>
+        <v>-0.979369200785799</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>-0.7148128122816902</v>
+        <v>-0.7148128122816904</v>
       </c>
       <c r="D102">
-        <v>-0.2545638709409363</v>
+        <v>-0.2545638709409356</v>
       </c>
       <c r="E102">
-        <v>0.6918451808898437</v>
+        <v>0.6918451808898438</v>
       </c>
       <c r="F102">
-        <v>-0.06427482578391235</v>
+        <v>-0.06427482578391219</v>
       </c>
       <c r="G102">
-        <v>-0.07165672137566573</v>
+        <v>-0.07165672137566581</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.5238647087282258</v>
+        <v>0.5238647087282282</v>
       </c>
       <c r="D103">
-        <v>-0.6467177905971262</v>
+        <v>-0.6467177905971275</v>
       </c>
       <c r="E103">
-        <v>-1.380834167622325</v>
+        <v>-1.380834167622324</v>
       </c>
       <c r="F103">
         <v>1.175096459633659</v>
       </c>
       <c r="G103">
-        <v>-0.0827068127684418</v>
+        <v>-0.08270681276844527</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.7302952766360624</v>
+        <v>0.7302952766360657</v>
       </c>
       <c r="D104">
-        <v>-1.759669094684473</v>
+        <v>-1.759669094684475</v>
       </c>
       <c r="E104">
-        <v>-1.313049135660765</v>
+        <v>-1.313049135660764</v>
       </c>
       <c r="F104">
-        <v>-1.143576514141235</v>
+        <v>-1.143576514141242</v>
       </c>
       <c r="G104">
-        <v>-2.107335993343949</v>
+        <v>-2.107335993343944</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-1.023893767038124</v>
+        <v>-1.023893767038122</v>
       </c>
       <c r="D105">
-        <v>-2.043566639374598</v>
+        <v>-2.043566639374597</v>
       </c>
       <c r="E105">
-        <v>-0.2161707547547338</v>
+        <v>-0.2161707547547317</v>
       </c>
       <c r="F105">
-        <v>2.326242220750987</v>
+        <v>2.326242220750983</v>
       </c>
       <c r="G105">
-        <v>-1.422355908156089</v>
+        <v>-1.422355908156098</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>1.288303430344283</v>
+        <v>1.288303430344284</v>
       </c>
       <c r="D106">
-        <v>0.5419400817910832</v>
+        <v>0.5419400817910855</v>
       </c>
       <c r="E106">
-        <v>0.9828537005224895</v>
+        <v>0.9828537005224894</v>
       </c>
       <c r="F106">
-        <v>1.169810311034547</v>
+        <v>1.16981031103455</v>
       </c>
       <c r="G106">
-        <v>0.9037440360615298</v>
+        <v>0.9037440360615254</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.9316233285907335</v>
+        <v>-0.9316233285907336</v>
       </c>
       <c r="D107">
-        <v>-0.7704741574921329</v>
+        <v>-0.770474157492132</v>
       </c>
       <c r="E107">
-        <v>0.9262610927387551</v>
+        <v>0.926261092738756</v>
       </c>
       <c r="F107">
-        <v>-0.04526310192808442</v>
+        <v>-0.04526310192808503</v>
       </c>
       <c r="G107">
-        <v>-0.3609643212864018</v>
+        <v>-0.3609643212864021</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>-0.8693480635500976</v>
+        <v>-0.8693480635500979</v>
       </c>
       <c r="D108">
-        <v>-1.125491408190761</v>
+        <v>-1.125491408190763</v>
       </c>
       <c r="E108">
-        <v>-0.3068417499279495</v>
+        <v>-0.3068417499279478</v>
       </c>
       <c r="F108">
-        <v>-0.2790485068511595</v>
+        <v>-0.2790485068511578</v>
       </c>
       <c r="G108">
-        <v>0.3493230293240117</v>
+        <v>0.3493230293240125</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.8198378124865806</v>
+        <v>-0.8198378124865805</v>
       </c>
       <c r="D109">
-        <v>-0.5800127245832706</v>
+        <v>-0.5800127245832724</v>
       </c>
       <c r="E109">
-        <v>-0.5215888943207674</v>
+        <v>-0.5215888943207667</v>
       </c>
       <c r="F109">
-        <v>-0.7446089165883039</v>
+        <v>-0.7446089165883026</v>
       </c>
       <c r="G109">
-        <v>0.2499461630685616</v>
+        <v>0.2499461630685645</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-0.7969446698899019</v>
+        <v>-0.7969446698899028</v>
       </c>
       <c r="D110">
-        <v>-0.7468309593569356</v>
+        <v>-0.7468309593569341</v>
       </c>
       <c r="E110">
-        <v>1.437138443390509</v>
+        <v>1.43713844339051</v>
       </c>
       <c r="F110">
-        <v>-0.2366145347792499</v>
+        <v>-0.2366145347792479</v>
       </c>
       <c r="G110">
-        <v>0.4089323931497035</v>
+        <v>0.4089323931497034</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.9006779061367641</v>
+        <v>-0.9006779061367647</v>
       </c>
       <c r="D111">
-        <v>0.708009426064155</v>
+        <v>0.7080094260641557</v>
       </c>
       <c r="E111">
-        <v>0.6911068645527808</v>
+        <v>0.6911068645527796</v>
       </c>
       <c r="F111">
-        <v>0.2074454318306426</v>
+        <v>0.2074454318306436</v>
       </c>
       <c r="G111">
-        <v>0.3242733474625401</v>
+        <v>0.324273347462539</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>1.147387834770621</v>
+        <v>1.147387834770622</v>
       </c>
       <c r="D112">
-        <v>-0.5897493895715835</v>
+        <v>-0.5897493895715809</v>
       </c>
       <c r="E112">
-        <v>1.657304026146362</v>
+        <v>1.657304026146364</v>
       </c>
       <c r="F112">
-        <v>0.1645926573784534</v>
+        <v>0.1645926573784563</v>
       </c>
       <c r="G112">
-        <v>0.7843974708748319</v>
+        <v>0.7843974708748307</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.7678688078788799</v>
+        <v>-0.7678688078788797</v>
       </c>
       <c r="D113">
-        <v>0.6206269576137902</v>
+        <v>0.6206269576137878</v>
       </c>
       <c r="E113">
-        <v>-0.8795550304718133</v>
+        <v>-0.8795550304718147</v>
       </c>
       <c r="F113">
-        <v>-0.861425595491675</v>
+        <v>-0.8614255954916739</v>
       </c>
       <c r="G113">
-        <v>0.350862249601964</v>
+        <v>0.350862249601968</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>4.727909130632116</v>
+        <v>4.727909130632121</v>
       </c>
       <c r="D114">
-        <v>-1.08775172796936</v>
+        <v>-1.087751727969356</v>
       </c>
       <c r="E114">
-        <v>1.950343803289057</v>
+        <v>1.95034380328906</v>
       </c>
       <c r="F114">
-        <v>-1.138636347628887</v>
+        <v>-1.138636347628889</v>
       </c>
       <c r="G114">
-        <v>-0.7134119411876964</v>
+        <v>-0.7134119411876921</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.5364076640042797</v>
+        <v>-0.5364076640042804</v>
       </c>
       <c r="D115">
-        <v>0.5021803483127115</v>
+        <v>0.5021803483127139</v>
       </c>
       <c r="E115">
-        <v>1.716050152662438</v>
+        <v>1.716050152662437</v>
       </c>
       <c r="F115">
-        <v>-0.195343729953911</v>
+        <v>-0.1953437299539114</v>
       </c>
       <c r="G115">
-        <v>-0.178788158090067</v>
+        <v>-0.1787881580900667</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.5139857686384605</v>
+        <v>-0.5139857686384602</v>
       </c>
       <c r="D116">
-        <v>-0.3491930848688545</v>
+        <v>-0.3491930848688557</v>
       </c>
       <c r="E116">
-        <v>-0.2345238486472466</v>
+        <v>-0.234523848647246</v>
       </c>
       <c r="F116">
-        <v>-0.5620804502143965</v>
+        <v>-0.5620804502143943</v>
       </c>
       <c r="G116">
-        <v>0.5212224135863904</v>
+        <v>0.5212224135863925</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-1.005991649624692</v>
+        <v>-1.005991649624693</v>
       </c>
       <c r="D117">
         <v>1.201111323783239</v>
       </c>
       <c r="E117">
-        <v>0.6012513050836539</v>
+        <v>0.6012513050836514</v>
       </c>
       <c r="F117">
-        <v>-0.1937333388059949</v>
+        <v>-0.1937333388059956</v>
       </c>
       <c r="G117">
-        <v>-0.2079030531510533</v>
+        <v>-0.2079030531510524</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.6031004552172223</v>
+        <v>0.6031004552172237</v>
       </c>
       <c r="D118">
-        <v>0.409839454744771</v>
+        <v>0.4098394547447708</v>
       </c>
       <c r="E118">
-        <v>-0.009497499731674793</v>
+        <v>-0.009497499731675383</v>
       </c>
       <c r="F118">
-        <v>-0.1834740881582309</v>
+        <v>-0.1834740881582302</v>
       </c>
       <c r="G118">
-        <v>0.2257732171257246</v>
+        <v>0.2257732171257258</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.3418377118532867</v>
+        <v>-0.3418377118532877</v>
       </c>
       <c r="D119">
-        <v>-1.300962783124299</v>
+        <v>-1.300962783124296</v>
       </c>
       <c r="E119">
-        <v>2.426099378451847</v>
+        <v>2.426099378451849</v>
       </c>
       <c r="F119">
-        <v>-0.479092099890192</v>
+        <v>-0.4790920998901892</v>
       </c>
       <c r="G119">
-        <v>0.598063958886336</v>
+        <v>0.5980639588863363</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.6747360204779952</v>
+        <v>-0.6747360204779949</v>
       </c>
       <c r="D120">
-        <v>0.6283126400837804</v>
+        <v>0.6283126400837791</v>
       </c>
       <c r="E120">
-        <v>-0.4239790852062554</v>
+        <v>-0.4239790852062568</v>
       </c>
       <c r="F120">
         <v>-0.6006520092101617</v>
       </c>
       <c r="G120">
-        <v>0.007299153212626646</v>
+        <v>0.007299153212629361</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>2.387891508117967</v>
+        <v>2.387891508117971</v>
       </c>
       <c r="D121">
-        <v>0.5737143516559384</v>
+        <v>0.5737143516559343</v>
       </c>
       <c r="E121">
-        <v>-2.864971026062112</v>
+        <v>-2.864971026062113</v>
       </c>
       <c r="F121">
-        <v>-0.953224272503613</v>
+        <v>-0.9532242725036141</v>
       </c>
       <c r="G121">
-        <v>-0.1560836232579159</v>
+        <v>-0.1560836232579102</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.6809671420522192</v>
+        <v>-0.6809671420522195</v>
       </c>
       <c r="D122">
-        <v>-0.7718568661767873</v>
+        <v>-0.7718568661767862</v>
       </c>
       <c r="E122">
-        <v>1.188373908076842</v>
+        <v>1.188373908076843</v>
       </c>
       <c r="F122">
-        <v>-1.000801245667056</v>
+        <v>-1.000801245667057</v>
       </c>
       <c r="G122">
-        <v>-0.4365569123185124</v>
+        <v>-0.4365569123185092</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.4159380854797207</v>
+        <v>0.4159380854797215</v>
       </c>
       <c r="D123">
-        <v>-0.1798589878434403</v>
+        <v>-0.1798589878434398</v>
       </c>
       <c r="E123">
-        <v>0.660157103237184</v>
+        <v>0.6601571032371845</v>
       </c>
       <c r="F123">
-        <v>-0.8057925636235773</v>
+        <v>-0.8057925636235771</v>
       </c>
       <c r="G123">
-        <v>-0.02431252060326358</v>
+        <v>-0.02431252060326064</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.834032991076332</v>
+        <v>-1.834032991076335</v>
       </c>
       <c r="D124">
-        <v>-0.2500552115875743</v>
+        <v>-0.2500552115875717</v>
       </c>
       <c r="E124">
-        <v>2.142111453072215</v>
+        <v>2.142111453072216</v>
       </c>
       <c r="F124">
-        <v>0.6318750771768248</v>
+        <v>0.6318750771768282</v>
       </c>
       <c r="G124">
-        <v>0.8791511114452124</v>
+        <v>0.8791511114452084</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>3.904884523928099</v>
+        <v>3.904884523928104</v>
       </c>
       <c r="D125">
-        <v>0.8946981291217835</v>
+        <v>0.8946981291217833</v>
       </c>
       <c r="E125">
-        <v>-0.8346619255473948</v>
+        <v>-0.8346619255473962</v>
       </c>
       <c r="F125">
-        <v>-1.059815892497068</v>
+        <v>-1.059815892497072</v>
       </c>
       <c r="G125">
-        <v>-0.9651150717129473</v>
+        <v>-0.9651150717129413</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>0.2808500888756235</v>
+        <v>0.2808500888756244</v>
       </c>
       <c r="D126">
         <v>0.4439549674265431</v>
       </c>
       <c r="E126">
-        <v>0.2545840856507451</v>
+        <v>0.2545840856507442</v>
       </c>
       <c r="F126">
-        <v>-0.8585752828943618</v>
+        <v>-0.8585752828943627</v>
       </c>
       <c r="G126">
-        <v>-0.2474136633783475</v>
+        <v>-0.2474136633783441</v>
       </c>
     </row>
   </sheetData>
